--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
@@ -441,7 +441,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -621,6 +621,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -630,7 +633,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -809,6 +812,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -852,7 +858,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1032,6 +1038,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1041,7 +1050,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1221,6 +1230,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>18201846.466008939</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18577567.752458461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1263,7 +1275,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1443,6 +1455,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1452,7 +1467,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1632,6 +1647,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>7763522.2841179464</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>8139243.5705674682</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1653,11 +1671,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99720192"/>
-        <c:axId val="103724160"/>
+        <c:axId val="470371328"/>
+        <c:axId val="470382080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99720192"/>
+        <c:axId val="470371328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1700,14 +1718,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103724160"/>
+        <c:crossAx val="470382080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103724160"/>
+        <c:axId val="470382080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1758,7 +1776,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99720192"/>
+        <c:crossAx val="470371328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1919,7 +1937,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2099,6 +2117,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-658295.54002827872</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-1831256.2144501123</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2113,8 +2134,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="424744832"/>
-        <c:axId val="399842304"/>
+        <c:axId val="625488256"/>
+        <c:axId val="620202624"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2139,7 +2160,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2319,6 +2340,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2328,7 +2352,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2508,6 +2532,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2524,11 +2551,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399531392"/>
-        <c:axId val="399840384"/>
+        <c:axId val="506750848"/>
+        <c:axId val="620200704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399531392"/>
+        <c:axId val="506750848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2571,14 +2598,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399840384"/>
+        <c:crossAx val="620200704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399840384"/>
+        <c:axId val="620200704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2629,12 +2656,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399531392"/>
+        <c:crossAx val="506750848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="399842304"/>
+        <c:axId val="620202624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2671,12 +2698,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="424744832"/>
+        <c:crossAx val="625488256"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="424744832"/>
+        <c:axId val="625488256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2685,7 +2712,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="399842304"/>
+        <c:crossAx val="620202624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3094,7 +3121,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5898,6 +5925,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63" spans="1:13" ht="12.75">
+      <c r="A63" s="11">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="12">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="12">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="13">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="13">
+        <v>-1831256.2144501123</v>
+      </c>
+      <c r="F63" s="14">
+        <v>-1435153.7473370298</v>
+      </c>
+      <c r="G63" s="14">
+        <v>10684880.666752618</v>
+      </c>
+      <c r="H63" s="14">
+        <v>13633907.975333851</v>
+      </c>
+      <c r="I63" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J63" s="14">
+        <v>18577567.752458461</v>
+      </c>
+      <c r="K63" s="14">
+        <v>8139243.5705674682</v>
+      </c>
+      <c r="L63" s="13">
+        <v>4943659.7771246117</v>
+      </c>
+      <c r="M63" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
@@ -441,7 +441,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -624,6 +624,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -633,7 +636,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -815,6 +818,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -858,7 +864,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1041,6 +1047,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1050,7 +1059,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1233,6 +1242,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>18577567.752458461</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16771822.603890486</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1275,7 +1287,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1458,6 +1470,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1467,7 +1482,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1650,6 +1665,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>8139243.5705674682</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6333498.4219994936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1671,11 +1689,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="470371328"/>
-        <c:axId val="470382080"/>
+        <c:axId val="508913152"/>
+        <c:axId val="521879552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="470371328"/>
+        <c:axId val="508913152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1718,14 +1736,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="470382080"/>
+        <c:crossAx val="521879552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="470382080"/>
+        <c:axId val="521879552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1776,7 +1794,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="470371328"/>
+        <c:crossAx val="508913152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1937,7 +1955,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2120,6 +2138,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-1831256.2144501123</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-629148.78444833402</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2134,8 +2155,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="625488256"/>
-        <c:axId val="620202624"/>
+        <c:axId val="567120256"/>
+        <c:axId val="554101376"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2160,7 +2181,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2343,6 +2364,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2352,7 +2376,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2535,6 +2559,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2551,11 +2578,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="506750848"/>
-        <c:axId val="620200704"/>
+        <c:axId val="548477952"/>
+        <c:axId val="554099840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="506750848"/>
+        <c:axId val="548477952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2598,14 +2625,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620200704"/>
+        <c:crossAx val="554099840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="620200704"/>
+        <c:axId val="554099840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2656,12 +2683,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="506750848"/>
+        <c:crossAx val="548477952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="620202624"/>
+        <c:axId val="554101376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2698,12 +2725,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625488256"/>
+        <c:crossAx val="567120256"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="625488256"/>
+        <c:axId val="567120256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2712,7 +2739,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="620202624"/>
+        <c:crossAx val="554101376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3121,7 +3148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5966,6 +5993,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:13" ht="12.75">
+      <c r="A64" s="11">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="12">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="12">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="13">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="13">
+        <v>-629148.78444833402</v>
+      </c>
+      <c r="F64" s="14">
+        <v>-568336.7554131808</v>
+      </c>
+      <c r="G64" s="14">
+        <v>10116543.911339438</v>
+      </c>
+      <c r="H64" s="14">
+        <v>11199014.042317541</v>
+      </c>
+      <c r="I64" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J64" s="14">
+        <v>16771822.603890486</v>
+      </c>
+      <c r="K64" s="14">
+        <v>6333498.4219994936</v>
+      </c>
+      <c r="L64" s="13">
+        <v>5572808.5615729457</v>
+      </c>
+      <c r="M64" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
@@ -441,7 +441,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -627,6 +627,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -636,7 +639,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -821,6 +824,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -864,7 +870,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1050,6 +1056,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1059,7 +1068,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1245,6 +1254,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>16771822.603890486</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16842638.102537446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1287,7 +1299,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1473,6 +1485,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1482,7 +1497,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1668,6 +1683,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>6333498.4219994936</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6404313.9206464533</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1689,11 +1707,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="508913152"/>
-        <c:axId val="521879552"/>
+        <c:axId val="387867776"/>
+        <c:axId val="387869312"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="508913152"/>
+        <c:axId val="387867776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1736,14 +1754,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521879552"/>
+        <c:crossAx val="387869312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="521879552"/>
+        <c:axId val="387869312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1794,7 +1812,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="508913152"/>
+        <c:crossAx val="387867776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1955,7 +1973,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2141,6 +2159,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-629148.78444833402</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-618346.8293536019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2155,8 +2176,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="567120256"/>
-        <c:axId val="554101376"/>
+        <c:axId val="485508608"/>
+        <c:axId val="485507072"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2181,7 +2202,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2367,6 +2388,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2376,7 +2400,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2562,6 +2586,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2578,11 +2605,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="548477952"/>
-        <c:axId val="554099840"/>
+        <c:axId val="429220224"/>
+        <c:axId val="429222144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="548477952"/>
+        <c:axId val="429220224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2625,14 +2652,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="554099840"/>
+        <c:crossAx val="429222144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="554099840"/>
+        <c:axId val="429222144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2683,12 +2710,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548477952"/>
+        <c:crossAx val="429220224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="554101376"/>
+        <c:axId val="485507072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2725,12 +2752,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567120256"/>
+        <c:crossAx val="485508608"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="567120256"/>
+        <c:axId val="485508608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2739,7 +2766,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="554101376"/>
+        <c:crossAx val="485507072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3148,7 +3175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -6034,6 +6061,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:13" ht="12.75">
+      <c r="A65" s="11">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="12">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="12">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="13">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="13">
+        <v>-618346.8293536019</v>
+      </c>
+      <c r="F65" s="14">
+        <v>-555068.98563595</v>
+      </c>
+      <c r="G65" s="14">
+        <v>9561474.9257034883</v>
+      </c>
+      <c r="H65" s="14">
+        <v>10651482.711610897</v>
+      </c>
+      <c r="I65" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J65" s="14">
+        <v>16842638.102537446</v>
+      </c>
+      <c r="K65" s="14">
+        <v>6404313.9206464533</v>
+      </c>
+      <c r="L65" s="13">
+        <v>6191155.3909265473</v>
+      </c>
+      <c r="M65" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">
